--- a/artfynd/A 59520-2025 artfynd.xlsx
+++ b/artfynd/A 59520-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1017,58 +1017,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124801325</v>
+        <v>130210282</v>
       </c>
       <c r="B5" t="n">
-        <v>110349</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219711</v>
+        <v>1968</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rökärret N om, Nrk</t>
+          <t>Klockhammar, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499946</v>
+        <v>499919</v>
       </c>
       <c r="R5" t="n">
-        <v>6581413</v>
+        <v>6581423</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,12 +1086,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,44 +1105,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>kalkpåverkad barrskog längs traktorväg</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mattias Sterner, Jessica Wiener, Madelen Andersson, Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124801329</v>
+        <v>130210285</v>
       </c>
       <c r="B6" t="n">
-        <v>100451</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,42 +1134,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rökärret N om, Nrk</t>
+          <t>Klockhammar, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499946</v>
+        <v>499880</v>
       </c>
       <c r="R6" t="n">
-        <v>6581413</v>
+        <v>6581433</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,12 +1192,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,39 +1211,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>kalkpåverkad barrskog längs traktorväg</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattias Sterner, Jessica Wiener, Madelen Andersson, Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128901302</v>
+        <v>130210284</v>
       </c>
       <c r="B7" t="n">
-        <v>92500</v>
+        <v>92596</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,27 +1257,24 @@
           <t>(Scop.) Fr.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rökärret, Ullavi klint, Nrk</t>
+          <t>Klockhammar, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499956</v>
+        <v>499901</v>
       </c>
       <c r="R7" t="n">
-        <v>6581409</v>
+        <v>6581432</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,27 +1298,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>3 st fruktkroppar ca 3 m söder om stigen i liten slänt.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,22 +1317,489 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124801325</v>
+      </c>
+      <c r="B8" t="n">
+        <v>110349</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rökärret N om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>499946</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6581413</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>kalkpåverkad barrskog längs traktorväg</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mattias Sterner, Jessica Wiener, Madelen Andersson, Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124801329</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rökärret N om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>499946</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6581413</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>kalkpåverkad barrskog längs traktorväg</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mattias Sterner, Jessica Wiener, Madelen Andersson, Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128901302</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92500</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rökärret, Ullavi klint, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>499956</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6581409</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3 st fruktkroppar ca 3 m söder om stigen i liten slänt.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Therese Steiner</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Therese Steiner</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130210300</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101022</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Klockhammar, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>499957</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6581373</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59520-2025 artfynd.xlsx
+++ b/artfynd/A 59520-2025 artfynd.xlsx
@@ -1017,37 +1017,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130210282</v>
+        <v>130210285</v>
       </c>
       <c r="B5" t="n">
-        <v>92957</v>
+        <v>92596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1968</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499919</v>
+        <v>499880</v>
       </c>
       <c r="R5" t="n">
-        <v>6581423</v>
+        <v>6581433</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,37 +1123,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130210285</v>
+        <v>130210282</v>
       </c>
       <c r="B6" t="n">
-        <v>92596</v>
+        <v>92957</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>1968</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499880</v>
+        <v>499919</v>
       </c>
       <c r="R6" t="n">
-        <v>6581433</v>
+        <v>6581423</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 59520-2025 artfynd.xlsx
+++ b/artfynd/A 59520-2025 artfynd.xlsx
@@ -1017,37 +1017,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130210285</v>
+        <v>130210282</v>
       </c>
       <c r="B5" t="n">
-        <v>92596</v>
+        <v>93044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>1968</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499880</v>
+        <v>499919</v>
       </c>
       <c r="R5" t="n">
-        <v>6581433</v>
+        <v>6581423</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,37 +1123,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130210282</v>
+        <v>130210285</v>
       </c>
       <c r="B6" t="n">
-        <v>92957</v>
+        <v>92683</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1968</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499919</v>
+        <v>499880</v>
       </c>
       <c r="R6" t="n">
-        <v>6581423</v>
+        <v>6581433</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1232,7 @@
         <v>130210284</v>
       </c>
       <c r="B7" t="n">
-        <v>92596</v>
+        <v>92683</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>130210300</v>
       </c>
       <c r="B11" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 59520-2025 artfynd.xlsx
+++ b/artfynd/A 59520-2025 artfynd.xlsx
@@ -1017,37 +1017,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130210282</v>
+        <v>130210285</v>
       </c>
       <c r="B5" t="n">
-        <v>93044</v>
+        <v>92683</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1968</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499919</v>
+        <v>499880</v>
       </c>
       <c r="R5" t="n">
-        <v>6581423</v>
+        <v>6581433</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,37 +1123,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130210285</v>
+        <v>130210282</v>
       </c>
       <c r="B6" t="n">
-        <v>92683</v>
+        <v>93044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>1968</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499880</v>
+        <v>499919</v>
       </c>
       <c r="R6" t="n">
-        <v>6581433</v>
+        <v>6581423</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 59520-2025 artfynd.xlsx
+++ b/artfynd/A 59520-2025 artfynd.xlsx
@@ -1017,37 +1017,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130210285</v>
+        <v>130210282</v>
       </c>
       <c r="B5" t="n">
-        <v>92683</v>
+        <v>93044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>1968</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499880</v>
+        <v>499919</v>
       </c>
       <c r="R5" t="n">
-        <v>6581433</v>
+        <v>6581423</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,37 +1123,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130210282</v>
+        <v>130210285</v>
       </c>
       <c r="B6" t="n">
-        <v>93044</v>
+        <v>92683</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1968</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499919</v>
+        <v>499880</v>
       </c>
       <c r="R6" t="n">
-        <v>6581423</v>
+        <v>6581433</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 59520-2025 artfynd.xlsx
+++ b/artfynd/A 59520-2025 artfynd.xlsx
@@ -1017,37 +1017,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130210282</v>
+        <v>130210285</v>
       </c>
       <c r="B5" t="n">
-        <v>93044</v>
+        <v>92686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1968</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499919</v>
+        <v>499880</v>
       </c>
       <c r="R5" t="n">
-        <v>6581423</v>
+        <v>6581433</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,37 +1123,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130210285</v>
+        <v>130210282</v>
       </c>
       <c r="B6" t="n">
-        <v>92683</v>
+        <v>93047</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>1968</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499880</v>
+        <v>499919</v>
       </c>
       <c r="R6" t="n">
-        <v>6581433</v>
+        <v>6581423</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1232,7 @@
         <v>130210284</v>
       </c>
       <c r="B7" t="n">
-        <v>92683</v>
+        <v>92686</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>130210300</v>
       </c>
       <c r="B11" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 59520-2025 artfynd.xlsx
+++ b/artfynd/A 59520-2025 artfynd.xlsx
@@ -1017,37 +1017,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130210285</v>
+        <v>130210282</v>
       </c>
       <c r="B5" t="n">
-        <v>92686</v>
+        <v>93073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>1968</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499880</v>
+        <v>499919</v>
       </c>
       <c r="R5" t="n">
-        <v>6581433</v>
+        <v>6581423</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,37 +1123,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130210282</v>
+        <v>130210285</v>
       </c>
       <c r="B6" t="n">
-        <v>93047</v>
+        <v>92712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1968</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499919</v>
+        <v>499880</v>
       </c>
       <c r="R6" t="n">
-        <v>6581423</v>
+        <v>6581433</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1232,7 @@
         <v>130210284</v>
       </c>
       <c r="B7" t="n">
-        <v>92686</v>
+        <v>92712</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>130210300</v>
       </c>
       <c r="B11" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 59520-2025 artfynd.xlsx
+++ b/artfynd/A 59520-2025 artfynd.xlsx
@@ -1020,7 +1020,7 @@
         <v>130210282</v>
       </c>
       <c r="B5" t="n">
-        <v>93073</v>
+        <v>93074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130210285</v>
       </c>
       <c r="B6" t="n">
-        <v>92712</v>
+        <v>92713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>130210284</v>
       </c>
       <c r="B7" t="n">
-        <v>92712</v>
+        <v>92713</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>130210300</v>
       </c>
       <c r="B11" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 59520-2025 artfynd.xlsx
+++ b/artfynd/A 59520-2025 artfynd.xlsx
@@ -1020,7 +1020,7 @@
         <v>130210282</v>
       </c>
       <c r="B5" t="n">
-        <v>93074</v>
+        <v>93075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130210285</v>
       </c>
       <c r="B6" t="n">
-        <v>92713</v>
+        <v>92714</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>130210284</v>
       </c>
       <c r="B7" t="n">
-        <v>92713</v>
+        <v>92714</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>130210300</v>
       </c>
       <c r="B11" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 59520-2025 artfynd.xlsx
+++ b/artfynd/A 59520-2025 artfynd.xlsx
@@ -1020,7 +1020,7 @@
         <v>130210282</v>
       </c>
       <c r="B5" t="n">
-        <v>93075</v>
+        <v>93077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130210285</v>
       </c>
       <c r="B6" t="n">
-        <v>92714</v>
+        <v>92716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>130210284</v>
       </c>
       <c r="B7" t="n">
-        <v>92714</v>
+        <v>92716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>130210300</v>
       </c>
       <c r="B11" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 59520-2025 artfynd.xlsx
+++ b/artfynd/A 59520-2025 artfynd.xlsx
@@ -1020,7 +1020,7 @@
         <v>130210282</v>
       </c>
       <c r="B5" t="n">
-        <v>93077</v>
+        <v>93081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130210285</v>
       </c>
       <c r="B6" t="n">
-        <v>92716</v>
+        <v>92720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>130210284</v>
       </c>
       <c r="B7" t="n">
-        <v>92716</v>
+        <v>92720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>130210300</v>
       </c>
       <c r="B11" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 59520-2025 artfynd.xlsx
+++ b/artfynd/A 59520-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>58220493</v>
+        <v>130210282</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>1968</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rökärret 3650/4050, Nrk</t>
+          <t>Klockhammar, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499827.2528223098</v>
+        <v>499919</v>
       </c>
       <c r="R2" t="n">
-        <v>6581367.338296373</v>
+        <v>6581423</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1986-05-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1986-05-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,12 +769,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -794,7 +784,7 @@
         <v>128901284</v>
       </c>
       <c r="B3" t="n">
-        <v>92845</v>
+        <v>93215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129063136</v>
+        <v>128901302</v>
       </c>
       <c r="B4" t="n">
-        <v>92508</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,22 +930,26 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Atlasruta 10F6a (Blackstahyttan), Nrk</t>
+          <t>Rökärret, Ullavi klint, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499858</v>
+        <v>499956</v>
       </c>
       <c r="R4" t="n">
-        <v>6581437</v>
+        <v>6581409</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,12 +973,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3 st fruktkroppar ca 3 m söder om stigen i liten slänt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,72 +1006,66 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130210282</v>
+        <v>129063136</v>
       </c>
       <c r="B5" t="n">
-        <v>93081</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1968</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Klockhammar, Nrk</t>
+          <t>Blackstahyttan, Atlasruta 10F6a (Blackstahyttan), Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499919</v>
+        <v>499858</v>
       </c>
       <c r="R5" t="n">
-        <v>6581423</v>
+        <v>6581437</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,17 +1089,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,28 +1103,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130210285</v>
+        <v>130210284</v>
       </c>
       <c r="B6" t="n">
-        <v>92720</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1162,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499880</v>
+        <v>499901</v>
       </c>
       <c r="R6" t="n">
-        <v>6581433</v>
+        <v>6581432</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130210284</v>
+        <v>130210285</v>
       </c>
       <c r="B7" t="n">
-        <v>92720</v>
+        <v>92869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499901</v>
+        <v>499880</v>
       </c>
       <c r="R7" t="n">
-        <v>6581432</v>
+        <v>6581433</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,16 +1342,11 @@
         <v>124801325</v>
       </c>
       <c r="B8" t="n">
-        <v>110349</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1449,22 +1448,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mattias Sterner, Jessica Wiener, Madelen Andersson, Michael Andersson</t>
+          <t>Michael Andersson, Madelen Andersson, Jessica Wiener, Mattias Sterner</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124801329</v>
+        <v>130210298</v>
       </c>
       <c r="B9" t="n">
-        <v>100451</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,45 +1466,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>219874</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rökärret N om, Nrk</t>
+          <t>Klockhammar, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499946</v>
+        <v>499776</v>
       </c>
       <c r="R9" t="n">
-        <v>6581413</v>
+        <v>6581404</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,12 +1524,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,84 +1543,66 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>kalkpåverkad barrskog längs traktorväg</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mattias Sterner, Jessica Wiener, Madelen Andersson, Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128901302</v>
+        <v>62304755</v>
       </c>
       <c r="B10" t="n">
-        <v>92500</v>
+        <v>102560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>222133</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rökärret, Ullavi klint, Nrk</t>
+          <t>Rökärret 3650/4050, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499956</v>
+        <v>499827</v>
       </c>
       <c r="R10" t="n">
-        <v>6581409</v>
+        <v>6581367</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1649,27 +1626,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>1981-01-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>3 st fruktkroppar ca 3 m söder om stigen i liten slänt.</t>
+          <t>1981-12-31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,29 +1640,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Gunnar Hallin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Gunnar Hallin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130210300</v>
+        <v>58220493</v>
       </c>
       <c r="B11" t="n">
-        <v>101146</v>
+        <v>104628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,41 +1669,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Klockhammar, Nrk</t>
+          <t>Rökärret 3650/4050, Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499957</v>
+        <v>499827</v>
       </c>
       <c r="R11" t="n">
-        <v>6581373</v>
+        <v>6581367</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1766,17 +1727,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>1986-05-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>1986-05-25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,15 +1747,358 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128901292</v>
+      </c>
+      <c r="B12" t="n">
+        <v>104627</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rökärret, Ullavi klint, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>499998</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6581406</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1 st ca 1 m hög under en gran ca 1 m söder om stigen.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124801329</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rökärret N om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>499946</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6581413</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>kalkpåverkad barrskog längs traktorväg</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Madelen Andersson, Jessica Wiener, Mattias Sterner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130210300</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Klockhammar, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>499957</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6581373</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59520-2025 artfynd.xlsx
+++ b/artfynd/A 59520-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210282</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128901284</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128901302</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129063136</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1230,6 +1255,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210284</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1336,6 +1366,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210285</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1452,6 +1487,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124801325</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1558,6 +1598,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210298</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1655,6 +1700,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62304755</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1756,6 +1806,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58220493</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1877,6 +1932,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128901292</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1993,6 +2053,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124801329</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2099,8 +2164,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210300</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>